--- a/data-sources/属性表/属性表.xlsx
+++ b/data-sources/属性表/属性表.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\策划\1.表格目录\XLS表格\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeName" sheetId="1" r:id="rId1"/>
@@ -2649,10 +2644,10 @@
     <t>攻击一定会暴击，暴击伤害降低{0}</t>
   </si>
   <si>
-    <t>近战技能范围效果增加</t>
-  </si>
-  <si>
-    <t>近战技能范围效果增加{0}</t>
+    <t>近战技能范围效果提高</t>
+  </si>
+  <si>
+    <t>近战技能范围效果提高{0}</t>
   </si>
   <si>
     <t>每秒生命回复</t>

--- a/data-sources/属性表/属性表.xlsx
+++ b/data-sources/属性表/属性表.xlsx
@@ -431,7 +431,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="967">
   <si>
     <t>属性名</t>
   </si>
@@ -2398,7 +2398,7 @@
     <t>范围效果提高{0}</t>
   </si>
   <si>
-    <t>冻结效果额外提高</t>
+    <t>冰冻效果额外提高</t>
   </si>
   <si>
     <t>冻结效果额外提高{0}</t>
@@ -2692,10 +2692,10 @@
     <t>天赋-太刀-移动速度转攻击伤害</t>
   </si>
   <si>
-    <t>天赋-通用-雷神</t>
-  </si>
-  <si>
-    <t>天赋-通用-雷神{0}</t>
+    <t>闪电伤害有几率附带触电累积</t>
+  </si>
+  <si>
+    <t>闪电伤害有{0}几率附带触电累积</t>
   </si>
   <si>
     <t>天赋-通用-火神</t>
@@ -3100,19 +3100,7 @@
     <t>法术技能等级增加{0}</t>
   </si>
   <si>
-    <t>物理抗性穿透{0}</t>
-  </si>
-  <si>
-    <t>火焰抗性穿透{0}</t>
-  </si>
-  <si>
-    <t>冰冷抗性穿透{0}</t>
-  </si>
-  <si>
-    <t>闪电抗性穿透{0}</t>
-  </si>
-  <si>
-    <t>混沌抗性穿透{0}</t>
+    <t>每3%投射物速度提供的1%投射物额外伤害，最多提供15%投射物额外伤害</t>
   </si>
   <si>
     <t>投射物速度转全局伤害</t>
@@ -3145,10 +3133,10 @@
     <t>近战暴击率提高{0}</t>
   </si>
   <si>
-    <t>进展暴击率额外提高</t>
-  </si>
-  <si>
-    <t>进展暴击率额外提高{0}</t>
+    <t>近战暴击率额外提高</t>
+  </si>
+  <si>
+    <t>近战暴击率额外提高{0}</t>
   </si>
   <si>
     <t>投射物暴击率提高</t>
@@ -3280,10 +3268,7 @@
     <t>攻击伤害命中时产生[瘫痪]效果\n[瘫痪]受到的攻击伤害额外提高15%，持续4秒</t>
   </si>
   <si>
-    <t>近战伤害每次命中获得[霸体]</t>
-  </si>
-  <si>
-    <t>近战伤害每次命中获得[霸体]\n[霸体]体型放大1%，攻击力提高1%，上限10层，持续时间4秒</t>
+    <t>混沌伤害额外提高1%，上限15层，持续4秒</t>
   </si>
   <si>
     <t>宠物-攻击必定软弱</t>
@@ -3344,6 +3329,9 @@
   </si>
   <si>
     <t>被辅助技能，击中中毒目标时，每层中毒效果伤害总增5%，上限5-8层</t>
+  </si>
+  <si>
+    <t>击中的火焰伤害使敌人的火焰抗性-12%，持续4秒</t>
   </si>
 </sst>
 </file>
@@ -4170,6 +4158,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -4213,9 +4204,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15432,500 +15420,500 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="7" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="35.5" style="17" customWidth="1"/>
-    <col min="3" max="3" width="56.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="56.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>643</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>10031</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>650</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>10032</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>653</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>10033</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>655</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>10034</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>657</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>10035</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>659</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="D8" s="1">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>10036</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>661</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="D9" s="1">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>10037</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>662</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>10038</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>663</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>10039</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>665</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D12" s="1">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>10040</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>667</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="D13" s="1">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>10041</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>669</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="D14" s="1">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>10042</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>671</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>10043</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>672</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>10044</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>673</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="3">
+      <c r="A18" s="4">
         <v>10045</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>10046</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>10047</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>676</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>10048</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>677</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>10049</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>678</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>10050</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>680</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>10051</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>682</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>10052</v>
       </c>
       <c r="B25" s="19" t="s">
@@ -15934,18 +15922,18 @@
       <c r="C25" s="19" t="s">
         <v>685</v>
       </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>10053</v>
       </c>
       <c r="B26" s="19" t="s">
@@ -15954,18 +15942,18 @@
       <c r="C26" s="19" t="s">
         <v>686</v>
       </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>10054</v>
       </c>
       <c r="B27" s="19" t="s">
@@ -15974,18 +15962,18 @@
       <c r="C27" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>10055</v>
       </c>
       <c r="B28" s="19" t="s">
@@ -15994,18 +15982,18 @@
       <c r="C28" s="19" t="s">
         <v>689</v>
       </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>10056</v>
       </c>
       <c r="B29" s="19" t="s">
@@ -16014,18 +16002,18 @@
       <c r="C29" s="19" t="s">
         <v>692</v>
       </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1">
-        <v>2</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>10057</v>
       </c>
       <c r="B30" s="19" t="s">
@@ -16034,698 +16022,698 @@
       <c r="C30" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="D30" s="1">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>10058</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1">
-        <v>2</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>10059</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>697</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>10060</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>699</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="D33" s="1">
-        <v>2</v>
-      </c>
-      <c r="E33" s="1">
-        <v>2</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>10061</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>701</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1">
-        <v>2</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>10062</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D35" s="1">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1">
-        <v>2</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>10063</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="D36" s="1">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1">
-        <v>2</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>10064</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="D37" s="1">
-        <v>2</v>
-      </c>
-      <c r="E37" s="1">
-        <v>2</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>10065</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>709</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="D38" s="1">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1">
-        <v>2</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>10066</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="D39" s="1">
-        <v>2</v>
-      </c>
-      <c r="E39" s="1">
-        <v>2</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="3">
+      <c r="A40" s="4">
         <v>10067</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="D40" s="1">
-        <v>2</v>
-      </c>
-      <c r="E40" s="1">
-        <v>2</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2">
+        <v>2</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>10068</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>713</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="D41" s="1">
-        <v>2</v>
-      </c>
-      <c r="E41" s="1">
-        <v>2</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>10069</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>715</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="D42" s="1">
-        <v>2</v>
-      </c>
-      <c r="E42" s="1">
-        <v>2</v>
-      </c>
-      <c r="F42" s="3" t="s">
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>10070</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>717</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="D43" s="1">
-        <v>2</v>
-      </c>
-      <c r="E43" s="1">
-        <v>2</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>10071</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>719</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="D44" s="1">
-        <v>2</v>
-      </c>
-      <c r="E44" s="1">
-        <v>2</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>10072</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>721</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D45" s="1">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1">
-        <v>2</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>10073</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>723</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="1">
-        <v>2</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>10074</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>725</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="D47" s="1">
-        <v>2</v>
-      </c>
-      <c r="E47" s="1">
-        <v>2</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="3">
+      <c r="A48" s="4">
         <v>10075</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>727</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="1">
-        <v>2</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="3">
+      <c r="A49" s="4">
         <v>10076</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>729</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="D49" s="1">
-        <v>2</v>
-      </c>
-      <c r="E49" s="1">
-        <v>2</v>
-      </c>
-      <c r="F49" s="3" t="s">
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="3">
+      <c r="A50" s="4">
         <v>10077</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>731</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="D50" s="2">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="3">
+      <c r="A51" s="4">
         <v>10078</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>733</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D51" s="1">
-        <v>2</v>
-      </c>
-      <c r="E51" s="1">
-        <v>2</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="3">
+      <c r="A52" s="4">
         <v>10079</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>735</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="D52" s="1">
-        <v>2</v>
-      </c>
-      <c r="E52" s="1">
-        <v>2</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="3">
+      <c r="A53" s="4">
         <v>10080</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="D53" s="1">
-        <v>2</v>
-      </c>
-      <c r="E53" s="1">
-        <v>2</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="3">
+      <c r="A54" s="4">
         <v>10081</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="D54" s="1">
-        <v>2</v>
-      </c>
-      <c r="E54" s="1">
-        <v>2</v>
-      </c>
-      <c r="F54" s="3" t="s">
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="3">
+      <c r="A55" s="4">
         <v>10082</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>741</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="D55" s="1">
-        <v>2</v>
-      </c>
-      <c r="E55" s="1">
-        <v>2</v>
-      </c>
-      <c r="F55" s="3" t="s">
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="3">
+      <c r="A56" s="4">
         <v>10083</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>743</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D56" s="1">
-        <v>2</v>
-      </c>
-      <c r="E56" s="1">
-        <v>2</v>
-      </c>
-      <c r="F56" s="3" t="s">
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="3">
+      <c r="A57" s="4">
         <v>10084</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="D57" s="1">
-        <v>2</v>
-      </c>
-      <c r="E57" s="1">
-        <v>2</v>
-      </c>
-      <c r="F57" s="3" t="s">
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="58" ht="34.5" spans="1:6">
-      <c r="A58" s="3">
+      <c r="A58" s="4">
         <v>10085</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>747</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="D58" s="1">
-        <v>2</v>
-      </c>
-      <c r="E58" s="1">
-        <v>2</v>
-      </c>
-      <c r="F58" s="3" t="s">
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="59" ht="34.5" spans="1:6">
-      <c r="A59" s="3">
+      <c r="A59" s="4">
         <v>10086</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>748</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="D59" s="1">
-        <v>2</v>
-      </c>
-      <c r="E59" s="1">
-        <v>2</v>
-      </c>
-      <c r="F59" s="3" t="s">
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="3">
+      <c r="A60" s="4">
         <v>10087</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>749</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="D60" s="1">
-        <v>2</v>
-      </c>
-      <c r="E60" s="1">
-        <v>2</v>
-      </c>
-      <c r="F60" s="3" t="s">
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="3">
+      <c r="A61" s="4">
         <v>10088</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>750</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="D61" s="1">
-        <v>2</v>
-      </c>
-      <c r="E61" s="1">
-        <v>2</v>
-      </c>
-      <c r="F61" s="3" t="s">
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" s="2">
+        <v>2</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="3">
+      <c r="A62" s="4">
         <v>10089</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>752</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="D62" s="1">
-        <v>2</v>
-      </c>
-      <c r="E62" s="1">
-        <v>2</v>
-      </c>
-      <c r="F62" s="3" t="s">
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="3">
+      <c r="A63" s="4">
         <v>10090</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>753</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="D63" s="1">
-        <v>2</v>
-      </c>
-      <c r="E63" s="1">
-        <v>2</v>
-      </c>
-      <c r="F63" s="3" t="s">
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="3">
+      <c r="A64" s="4">
         <v>10091</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>755</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="D64" s="1">
-        <v>2</v>
-      </c>
-      <c r="E64" s="1">
-        <v>2</v>
-      </c>
-      <c r="F64" s="3" t="s">
+      <c r="D64" s="2">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="3">
+      <c r="A65" s="4">
         <v>10092</v>
       </c>
       <c r="B65" s="19" t="s">
@@ -16734,1733 +16722,1653 @@
       <c r="C65" s="19" t="s">
         <v>758</v>
       </c>
-      <c r="D65" s="1">
-        <v>2</v>
-      </c>
-      <c r="E65" s="1">
-        <v>2</v>
-      </c>
-      <c r="F65" s="3" t="s">
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2">
+        <v>2</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="3">
+      <c r="A66" s="4">
         <v>10093</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>759</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="D66" s="1">
-        <v>2</v>
-      </c>
-      <c r="E66" s="1">
-        <v>2</v>
-      </c>
-      <c r="F66" s="3" t="s">
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="3">
+      <c r="A67" s="4">
         <v>10094</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>761</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="D67" s="1">
-        <v>2</v>
-      </c>
-      <c r="E67" s="1">
-        <v>2</v>
-      </c>
-      <c r="F67" s="3" t="s">
+      <c r="D67" s="2">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2">
+        <v>2</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="3">
+      <c r="A68" s="4">
         <v>10095</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>763</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D68" s="1">
-        <v>2</v>
-      </c>
-      <c r="E68" s="1">
-        <v>2</v>
-      </c>
-      <c r="F68" s="3" t="s">
+      <c r="D68" s="2">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="3">
+      <c r="A69" s="4">
         <v>10096</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>765</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D69" s="1">
-        <v>2</v>
-      </c>
-      <c r="E69" s="1">
-        <v>2</v>
-      </c>
-      <c r="F69" s="3" t="s">
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="3">
+      <c r="A70" s="4">
         <v>10097</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>767</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C70" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="D70" s="1">
-        <v>2</v>
-      </c>
-      <c r="E70" s="1">
-        <v>2</v>
-      </c>
-      <c r="F70" s="3" t="s">
+      <c r="D70" s="2">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="3">
+      <c r="A71" s="4">
         <v>10098</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>769</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="D71" s="1">
-        <v>2</v>
-      </c>
-      <c r="E71" s="1">
-        <v>2</v>
-      </c>
-      <c r="F71" s="3" t="s">
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="3">
+      <c r="A72" s="4">
         <v>10099</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>771</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="D72" s="1">
-        <v>2</v>
-      </c>
-      <c r="E72" s="1">
-        <v>2</v>
-      </c>
-      <c r="F72" s="3" t="s">
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2">
+        <v>2</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="3">
+      <c r="A73" s="4">
         <v>10100</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>773</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="D73" s="1">
-        <v>2</v>
-      </c>
-      <c r="E73" s="1">
-        <v>2</v>
-      </c>
-      <c r="F73" s="3" t="s">
+      <c r="D73" s="2">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="3">
+      <c r="A74" s="4">
         <v>10101</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>775</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D74" s="1">
-        <v>2</v>
-      </c>
-      <c r="E74" s="1">
-        <v>2</v>
-      </c>
-      <c r="F74" s="3" t="s">
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="3">
+      <c r="A75" s="4">
         <v>10102</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>777</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="D75" s="1">
-        <v>2</v>
-      </c>
-      <c r="E75" s="1">
-        <v>2</v>
-      </c>
-      <c r="F75" s="3" t="s">
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="3">
+      <c r="A76" s="4">
         <v>10103</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>779</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D76" s="1">
-        <v>2</v>
-      </c>
-      <c r="E76" s="1">
-        <v>2</v>
-      </c>
-      <c r="F76" s="3" t="s">
+      <c r="D76" s="2">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="3">
+      <c r="A77" s="4">
         <v>10104</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>780</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="D77" s="1">
-        <v>2</v>
-      </c>
-      <c r="E77" s="1">
-        <v>2</v>
-      </c>
-      <c r="F77" s="3" t="s">
+      <c r="D77" s="2">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2">
+        <v>2</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="3">
+      <c r="A78" s="4">
         <v>10105</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>781</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="D78" s="1">
-        <v>2</v>
-      </c>
-      <c r="E78" s="1">
-        <v>2</v>
-      </c>
-      <c r="F78" s="3" t="s">
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>10106</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>782</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="D79" s="1">
-        <v>2</v>
-      </c>
-      <c r="E79" s="2">
-        <v>2</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="D79" s="2">
+        <v>2</v>
+      </c>
+      <c r="E79" s="3">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>10107</v>
       </c>
       <c r="B80" s="17" t="s">
         <v>784</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="D80" s="1">
-        <v>2</v>
-      </c>
-      <c r="E80" s="2">
-        <v>2</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="3">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>10108</v>
       </c>
       <c r="B81" s="17" t="s">
         <v>786</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="D81" s="1">
-        <v>2</v>
-      </c>
-      <c r="E81" s="2">
-        <v>2</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>10109</v>
       </c>
       <c r="B82" s="17" t="s">
         <v>788</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="D82" s="1">
-        <v>2</v>
-      </c>
-      <c r="E82" s="2">
-        <v>2</v>
-      </c>
-      <c r="F82" s="1" t="s">
+      <c r="D82" s="2">
+        <v>2</v>
+      </c>
+      <c r="E82" s="3">
+        <v>2</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>10110</v>
       </c>
       <c r="B83" s="17" t="s">
         <v>790</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="D83" s="1">
-        <v>2</v>
-      </c>
-      <c r="E83" s="2">
-        <v>2</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="D83" s="2">
+        <v>2</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>10111</v>
       </c>
       <c r="B84" s="17" t="s">
         <v>792</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="D84" s="1">
-        <v>2</v>
-      </c>
-      <c r="E84" s="2">
-        <v>2</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="3">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>10112</v>
       </c>
       <c r="B85" s="17" t="s">
         <v>794</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="D85" s="1">
-        <v>2</v>
-      </c>
-      <c r="E85" s="2">
-        <v>2</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="D85" s="2">
+        <v>2</v>
+      </c>
+      <c r="E85" s="3">
+        <v>2</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>10113</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>796</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="D86" s="1">
-        <v>2</v>
-      </c>
-      <c r="E86" s="2">
-        <v>2</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="D86" s="2">
+        <v>2</v>
+      </c>
+      <c r="E86" s="3">
+        <v>2</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>10114</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>798</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="D87" s="1">
-        <v>2</v>
-      </c>
-      <c r="E87" s="2">
-        <v>2</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="3">
+        <v>2</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>10116</v>
       </c>
       <c r="B88" s="17" t="s">
         <v>800</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="D88" s="1">
-        <v>2</v>
-      </c>
-      <c r="E88" s="2">
-        <v>2</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="D88" s="2">
+        <v>2</v>
+      </c>
+      <c r="E88" s="3">
+        <v>2</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>10117</v>
       </c>
       <c r="B89" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="D89" s="1">
-        <v>0</v>
-      </c>
-      <c r="E89" s="2">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1" t="s">
+      <c r="D89" s="2">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>10118</v>
       </c>
       <c r="B90" s="17" t="s">
         <v>804</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D90" s="1">
-        <v>2</v>
-      </c>
-      <c r="E90" s="2">
-        <v>2</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="3">
+        <v>2</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>10119</v>
       </c>
       <c r="B91" s="17" t="s">
         <v>806</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="D91" s="1">
-        <v>2</v>
-      </c>
-      <c r="E91" s="2">
-        <v>2</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="D91" s="2">
+        <v>2</v>
+      </c>
+      <c r="E91" s="3">
+        <v>2</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>10120</v>
       </c>
       <c r="B92" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="D92" s="1">
-        <v>2</v>
-      </c>
-      <c r="E92" s="2">
-        <v>2</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="D92" s="2">
+        <v>2</v>
+      </c>
+      <c r="E92" s="3">
+        <v>2</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>10121</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>809</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="D93" s="1">
-        <v>2</v>
-      </c>
-      <c r="E93" s="2">
-        <v>2</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="D93" s="2">
+        <v>2</v>
+      </c>
+      <c r="E93" s="3">
+        <v>2</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>10122</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>811</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="D94" s="1">
-        <v>0</v>
-      </c>
-      <c r="E94" s="2">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="D94" s="2">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>10123</v>
       </c>
       <c r="B95" s="17" t="s">
         <v>813</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="D95" s="1">
-        <v>2</v>
-      </c>
-      <c r="E95" s="2">
-        <v>2</v>
-      </c>
-      <c r="F95" s="1" t="s">
+      <c r="D95" s="2">
+        <v>2</v>
+      </c>
+      <c r="E95" s="3">
+        <v>2</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>10124</v>
       </c>
       <c r="B96" s="17" t="s">
         <v>815</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="D96" s="1">
-        <v>2</v>
-      </c>
-      <c r="E96" s="2">
-        <v>2</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>10125</v>
       </c>
       <c r="B97" s="17" t="s">
         <v>817</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="D97" s="1">
-        <v>2</v>
-      </c>
-      <c r="E97" s="2">
-        <v>2</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="D97" s="2">
+        <v>2</v>
+      </c>
+      <c r="E97" s="3">
+        <v>2</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>10126</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>804</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D98" s="1">
-        <v>2</v>
-      </c>
-      <c r="E98" s="2">
-        <v>2</v>
-      </c>
-      <c r="F98" s="1" t="s">
+      <c r="D98" s="2">
+        <v>2</v>
+      </c>
+      <c r="E98" s="3">
+        <v>2</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>10127</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>819</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="D99" s="1">
-        <v>2</v>
-      </c>
-      <c r="E99" s="2">
-        <v>2</v>
-      </c>
-      <c r="F99" s="1" t="s">
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="3">
+        <v>2</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>10128</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>821</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="D100" s="1">
-        <v>2</v>
-      </c>
-      <c r="E100" s="2">
-        <v>2</v>
-      </c>
-      <c r="F100" s="1" t="s">
+      <c r="D100" s="2">
+        <v>2</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>10129</v>
       </c>
       <c r="B101" s="17" t="s">
         <v>823</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="D101" s="1">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2">
-        <v>0</v>
-      </c>
-      <c r="F101" s="1" t="s">
+      <c r="D101" s="2">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>10130</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>825</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="D102" s="1">
-        <v>2</v>
-      </c>
-      <c r="E102" s="2">
-        <v>2</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="D102" s="2">
+        <v>2</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>10131</v>
       </c>
       <c r="B103" s="17" t="s">
         <v>827</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="D103" s="1">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2">
-        <v>0</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>10132</v>
       </c>
       <c r="B104" s="17" t="s">
         <v>829</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="D104" s="1">
-        <v>2</v>
-      </c>
-      <c r="E104" s="2">
-        <v>2</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="D104" s="2">
+        <v>2</v>
+      </c>
+      <c r="E104" s="3">
+        <v>2</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>10134</v>
       </c>
       <c r="B105" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="D105" s="1">
-        <v>2</v>
-      </c>
-      <c r="E105" s="2">
-        <v>2</v>
-      </c>
-      <c r="F105" s="1" t="s">
+      <c r="D105" s="2">
+        <v>2</v>
+      </c>
+      <c r="E105" s="3">
+        <v>2</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>10135</v>
       </c>
       <c r="B106" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="D106" s="1">
-        <v>2</v>
-      </c>
-      <c r="E106" s="2">
-        <v>2</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="3">
+        <v>2</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>10136</v>
       </c>
       <c r="B107" s="17" t="s">
         <v>835</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="D107" s="1">
-        <v>2</v>
-      </c>
-      <c r="E107" s="2">
-        <v>2</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="D107" s="2">
+        <v>2</v>
+      </c>
+      <c r="E107" s="3">
+        <v>2</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>10137</v>
       </c>
       <c r="B108" s="17" t="s">
         <v>837</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="D108" s="1">
-        <v>2</v>
-      </c>
-      <c r="E108" s="2">
-        <v>2</v>
-      </c>
-      <c r="F108" s="1" t="s">
+      <c r="D108" s="2">
+        <v>2</v>
+      </c>
+      <c r="E108" s="3">
+        <v>2</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>10138</v>
       </c>
       <c r="B109" s="17" t="s">
         <v>839</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="D109" s="1">
-        <v>2</v>
-      </c>
-      <c r="E109" s="2">
-        <v>2</v>
-      </c>
-      <c r="F109" s="1" t="s">
+      <c r="D109" s="2">
+        <v>2</v>
+      </c>
+      <c r="E109" s="3">
+        <v>2</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>10139</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>841</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="D110" s="1">
-        <v>0</v>
-      </c>
-      <c r="E110" s="2">
-        <v>0</v>
-      </c>
-      <c r="F110" s="1" t="s">
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>10140</v>
       </c>
       <c r="B111" s="17" t="s">
         <v>843</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="D111" s="1">
-        <v>2</v>
-      </c>
-      <c r="E111" s="2">
-        <v>2</v>
-      </c>
-      <c r="F111" s="1" t="s">
+      <c r="D111" s="2">
+        <v>2</v>
+      </c>
+      <c r="E111" s="3">
+        <v>2</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>10141</v>
       </c>
       <c r="B112" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="D112" s="1">
-        <v>0</v>
-      </c>
-      <c r="E112" s="2">
-        <v>0</v>
-      </c>
-      <c r="F112" s="1" t="s">
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>10142</v>
       </c>
       <c r="B113" s="17" t="s">
         <v>847</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="D113" s="1">
-        <v>2</v>
-      </c>
-      <c r="E113" s="2">
-        <v>2</v>
-      </c>
-      <c r="F113" s="1" t="s">
+      <c r="D113" s="2">
+        <v>2</v>
+      </c>
+      <c r="E113" s="3">
+        <v>2</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>10143</v>
       </c>
       <c r="B114" s="17" t="s">
         <v>849</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="D114" s="1">
-        <v>2</v>
-      </c>
-      <c r="E114" s="2">
-        <v>2</v>
-      </c>
-      <c r="F114" s="1" t="s">
+      <c r="D114" s="2">
+        <v>2</v>
+      </c>
+      <c r="E114" s="3">
+        <v>2</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>10144</v>
       </c>
       <c r="B115" s="17" t="s">
         <v>851</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="D115" s="1">
-        <v>2</v>
-      </c>
-      <c r="E115" s="2">
-        <v>2</v>
-      </c>
-      <c r="F115" s="1" t="s">
+      <c r="D115" s="2">
+        <v>2</v>
+      </c>
+      <c r="E115" s="3">
+        <v>2</v>
+      </c>
+      <c r="F115" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>10145</v>
       </c>
       <c r="B116" s="17" t="s">
         <v>853</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="2">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1" t="s">
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>10146</v>
       </c>
       <c r="B117" s="17" t="s">
         <v>855</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="D117" s="1">
-        <v>2</v>
-      </c>
-      <c r="E117" s="2">
-        <v>2</v>
-      </c>
-      <c r="F117" s="1" t="s">
+      <c r="D117" s="2">
+        <v>2</v>
+      </c>
+      <c r="E117" s="3">
+        <v>2</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>10147</v>
       </c>
       <c r="B118" s="17" t="s">
         <v>857</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="D118" s="1">
-        <v>2</v>
-      </c>
-      <c r="E118" s="2">
-        <v>2</v>
-      </c>
-      <c r="F118" s="1" t="s">
+      <c r="D118" s="2">
+        <v>2</v>
+      </c>
+      <c r="E118" s="3">
+        <v>2</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>10148</v>
       </c>
       <c r="B119" s="17" t="s">
         <v>859</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="D119" s="1">
-        <v>0</v>
-      </c>
-      <c r="E119" s="2">
-        <v>0</v>
-      </c>
-      <c r="F119" s="1" t="s">
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" s="3">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>10149</v>
       </c>
       <c r="B120" s="17" t="s">
         <v>861</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="D120" s="1">
-        <v>0</v>
-      </c>
-      <c r="E120" s="2">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1" t="s">
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>10150</v>
       </c>
       <c r="B121" s="17" t="s">
         <v>863</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="D121" s="1">
-        <v>0</v>
-      </c>
-      <c r="E121" s="2">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1" t="s">
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>10151</v>
       </c>
       <c r="B122" s="17" t="s">
         <v>865</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="D122" s="1">
-        <v>0</v>
-      </c>
-      <c r="E122" s="2">
-        <v>0</v>
-      </c>
-      <c r="F122" s="1" t="s">
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>10152</v>
       </c>
       <c r="B123" s="17" t="s">
         <v>867</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="D123" s="1">
-        <v>0</v>
-      </c>
-      <c r="E123" s="2">
-        <v>0</v>
-      </c>
-      <c r="F123" s="1" t="s">
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>10153</v>
       </c>
       <c r="B124" s="17" t="s">
         <v>869</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="D124" s="1">
-        <v>0</v>
-      </c>
-      <c r="E124" s="2">
-        <v>0</v>
-      </c>
-      <c r="F124" s="1" t="s">
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>10154</v>
       </c>
       <c r="B125" s="17" t="s">
         <v>871</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="D125" s="1">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2">
-        <v>0</v>
-      </c>
-      <c r="F125" s="1" t="s">
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>10155</v>
       </c>
       <c r="B126" s="17" t="s">
         <v>873</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="D126" s="1">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2">
-        <v>0</v>
-      </c>
-      <c r="F126" s="1" t="s">
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>10156</v>
       </c>
       <c r="B127" s="17" t="s">
         <v>875</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="D127" s="1">
-        <v>0</v>
-      </c>
-      <c r="E127" s="2">
-        <v>0</v>
-      </c>
-      <c r="F127" s="1" t="s">
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" s="3">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>10157</v>
       </c>
       <c r="B128" s="17" t="s">
         <v>877</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="D128" s="1">
-        <v>0</v>
-      </c>
-      <c r="E128" s="2">
-        <v>0</v>
-      </c>
-      <c r="F128" s="1" t="s">
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>10158</v>
       </c>
       <c r="B129" s="17" t="s">
         <v>879</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="D129" s="1">
-        <v>0</v>
-      </c>
-      <c r="E129" s="2">
-        <v>0</v>
-      </c>
-      <c r="F129" s="1" t="s">
+      <c r="D129" s="2">
+        <v>0</v>
+      </c>
+      <c r="E129" s="3">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>10159</v>
       </c>
       <c r="B130" s="17" t="s">
         <v>881</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="D130" s="1">
-        <v>0</v>
-      </c>
-      <c r="E130" s="2">
-        <v>0</v>
-      </c>
-      <c r="F130" s="1" t="s">
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130" s="3">
+        <v>0</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>10160</v>
       </c>
       <c r="B131" s="17" t="s">
         <v>883</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="D131" s="1">
-        <v>0</v>
-      </c>
-      <c r="E131" s="2">
-        <v>0</v>
-      </c>
-      <c r="F131" s="1" t="s">
+      <c r="D131" s="2">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>10161</v>
       </c>
       <c r="B132" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="D132" s="1">
-        <v>0</v>
-      </c>
-      <c r="E132" s="2">
-        <v>0</v>
-      </c>
-      <c r="F132" s="1" t="s">
+      <c r="D132" s="2">
+        <v>0</v>
+      </c>
+      <c r="E132" s="3">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="1">
+    <row r="133" customHeight="1" spans="1:6">
+      <c r="A133" s="2">
         <v>10162</v>
       </c>
       <c r="B133" s="17" t="s">
         <v>887</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="D133" s="1">
-        <v>0</v>
-      </c>
-      <c r="E133" s="2">
-        <v>0</v>
-      </c>
-      <c r="F133" s="1" t="s">
+      <c r="D133" s="2">
+        <v>0</v>
+      </c>
+      <c r="E133" s="3">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="1">
-        <v>10163</v>
+    <row r="134" customHeight="1" spans="1:6">
+      <c r="A134" s="2">
+        <v>10167</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="C134" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="D134" s="1">
-        <v>2</v>
-      </c>
-      <c r="E134" s="1">
-        <v>2</v>
-      </c>
-      <c r="F134" s="1" t="s">
+      <c r="C134" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="D134" s="2">
+        <v>2</v>
+      </c>
+      <c r="E134" s="2">
+        <v>2</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="1">
-        <v>10164</v>
+      <c r="A135" s="2">
+        <v>10168</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="C135" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="D135" s="1">
-        <v>2</v>
-      </c>
-      <c r="E135" s="1">
-        <v>2</v>
-      </c>
-      <c r="F135" s="1" t="s">
+      <c r="C135" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D135" s="2">
+        <v>2</v>
+      </c>
+      <c r="E135" s="2">
+        <v>2</v>
+      </c>
+      <c r="F135" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="1">
-        <v>10165</v>
+      <c r="A136" s="2">
+        <v>10169</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="D136" s="1">
-        <v>2</v>
-      </c>
-      <c r="E136" s="1">
-        <v>2</v>
-      </c>
-      <c r="F136" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="D136" s="2">
+        <v>2</v>
+      </c>
+      <c r="E136" s="2">
+        <v>2</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="1">
-        <v>10166</v>
+      <c r="A137" s="2">
+        <v>10170</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="D137" s="1">
-        <v>2</v>
-      </c>
-      <c r="E137" s="1">
-        <v>2</v>
-      </c>
-      <c r="F137" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D137" s="2">
+        <v>2</v>
+      </c>
+      <c r="E137" s="2">
+        <v>2</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="1">
-        <v>10167</v>
+      <c r="A138" s="2">
+        <v>10171</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="D138" s="1">
-        <v>2</v>
-      </c>
-      <c r="E138" s="1">
-        <v>2</v>
-      </c>
-      <c r="F138" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="D138" s="2">
+        <v>2</v>
+      </c>
+      <c r="E138" s="2">
+        <v>2</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="1">
-        <v>10168</v>
+      <c r="A139" s="2">
+        <v>10172</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="D139" s="1">
-        <v>2</v>
-      </c>
-      <c r="E139" s="1">
-        <v>2</v>
-      </c>
-      <c r="F139" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="D139" s="2">
+        <v>2</v>
+      </c>
+      <c r="E139" s="2">
+        <v>2</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="1">
-        <v>10169</v>
+      <c r="A140" s="2">
+        <v>10173</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="D140" s="1">
-        <v>2</v>
-      </c>
-      <c r="E140" s="1">
-        <v>2</v>
-      </c>
-      <c r="F140" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="D140" s="2">
+        <v>2</v>
+      </c>
+      <c r="E140" s="2">
+        <v>2</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="1">
-        <v>10170</v>
+      <c r="A141" s="2">
+        <v>10174</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>898</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="D141" s="1">
-        <v>2</v>
-      </c>
-      <c r="E141" s="1">
-        <v>2</v>
-      </c>
-      <c r="F141" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D141" s="2">
+        <v>2</v>
+      </c>
+      <c r="E141" s="2">
+        <v>2</v>
+      </c>
+      <c r="F141" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="1">
-        <v>10171</v>
+      <c r="A142" s="2">
+        <v>10175</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>900</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="D142" s="1">
-        <v>2</v>
-      </c>
-      <c r="E142" s="1">
-        <v>2</v>
-      </c>
-      <c r="F142" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="D142" s="2">
+        <v>2</v>
+      </c>
+      <c r="E142" s="2">
+        <v>2</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="1">
-        <v>10172</v>
+      <c r="A143" s="2">
+        <v>10176</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>902</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="D143" s="1">
-        <v>2</v>
-      </c>
-      <c r="E143" s="1">
-        <v>2</v>
-      </c>
-      <c r="F143" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="D143" s="2">
+        <v>2</v>
+      </c>
+      <c r="E143" s="2">
+        <v>2</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="1">
-        <v>10173</v>
+      <c r="A144" s="2">
+        <v>10177</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>904</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="D144" s="1">
-        <v>2</v>
-      </c>
-      <c r="E144" s="1">
-        <v>2</v>
-      </c>
-      <c r="F144" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="D144" s="2">
+        <v>2</v>
+      </c>
+      <c r="E144" s="2">
+        <v>2</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" s="1" customFormat="1" spans="1:6">
       <c r="A145" s="1">
-        <v>10174</v>
-      </c>
-      <c r="B145" s="17" t="s">
-        <v>906</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="D145" s="1">
-        <v>2</v>
-      </c>
-      <c r="E145" s="1">
-        <v>2</v>
-      </c>
-      <c r="F145" s="1" t="s">
+        <v>10178</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="D145" s="2">
+        <v>2</v>
+      </c>
+      <c r="E145" s="2">
+        <v>2</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" s="1" customFormat="1" spans="1:6">
       <c r="A146" s="1">
-        <v>10175</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>908</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="D146" s="1">
-        <v>2</v>
-      </c>
-      <c r="E146" s="1">
-        <v>2</v>
-      </c>
-      <c r="F146" s="1" t="s">
+        <v>10179</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="D146" s="2">
+        <v>2</v>
+      </c>
+      <c r="E146" s="2">
+        <v>2</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" s="1" customFormat="1" spans="1:6">
       <c r="A147" s="1">
-        <v>10176</v>
-      </c>
-      <c r="B147" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="D147" s="1">
-        <v>2</v>
-      </c>
-      <c r="E147" s="1">
-        <v>2</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" s="1">
-        <v>10177</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>912</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="D148" s="1">
-        <v>2</v>
-      </c>
-      <c r="E148" s="1">
-        <v>2</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="149" s="16" customFormat="1" spans="1:6">
-      <c r="A149" s="16">
-        <v>10178</v>
-      </c>
-      <c r="B149" s="1" t="s">
+        <v>10180</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C149" s="16" t="s">
+      <c r="C147" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="D149" s="1">
-        <v>2</v>
-      </c>
-      <c r="E149" s="1">
-        <v>2</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="150" s="16" customFormat="1" spans="1:6">
-      <c r="A150" s="16">
-        <v>10179</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="C150" s="16" t="s">
-        <v>917</v>
-      </c>
-      <c r="D150" s="1">
-        <v>2</v>
-      </c>
-      <c r="E150" s="1">
-        <v>2</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="151" s="16" customFormat="1" spans="1:6">
-      <c r="A151" s="16">
-        <v>10180</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>918</v>
-      </c>
-      <c r="C151" s="16" t="s">
-        <v>919</v>
-      </c>
-      <c r="D151" s="1">
-        <v>2</v>
-      </c>
-      <c r="E151" s="1">
-        <v>2</v>
-      </c>
-      <c r="F151" s="1" t="s">
+      <c r="D147" s="2">
+        <v>2</v>
+      </c>
+      <c r="E147" s="2">
+        <v>2</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>652</v>
       </c>
     </row>
@@ -18477,1135 +18385,1169 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="66.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="64.125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19.75" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="22.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="66.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="64.125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="19.75" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="11">
+        <v>2110000010</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="33" spans="1:5">
+      <c r="A5" s="13">
+        <v>2110000011</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="33" spans="1:5">
+      <c r="A6" s="15">
+        <v>2110000012</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>919</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>919</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="13">
+        <v>2110000020</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>920</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10">
-        <v>2110000010</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>921</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="33" spans="1:5">
+      <c r="A8" s="15">
+        <v>2110000021</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>922</v>
       </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="33" spans="1:5">
-      <c r="A5" s="12">
-        <v>2110000011</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="C8" s="16" t="s">
+        <v>922</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="13">
+        <v>2110000030</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>923</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>923</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="33" spans="1:5">
-      <c r="A6" s="14">
-        <v>2110000012</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>923</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>923</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="12">
-        <v>2110000020</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>924</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="33" spans="1:5">
+      <c r="A10" s="15">
+        <v>2110000031</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>925</v>
       </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="33" spans="1:5">
-      <c r="A8" s="14">
-        <v>2110000021</v>
-      </c>
-      <c r="B8" s="15" t="s">
+      <c r="C10" s="16" t="s">
+        <v>925</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="13">
+        <v>2110000040</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="12">
-        <v>2110000030</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="15">
+        <v>2114000020</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>927</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C12" s="16" t="s">
+        <v>927</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="33" spans="1:5">
+      <c r="A13" s="13">
+        <v>2120000010</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>928</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="33" spans="1:5">
-      <c r="A10" s="14">
-        <v>2110000031</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="C13" s="14" t="s">
+        <v>928</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="33" spans="1:5">
+      <c r="A14" s="15">
+        <v>2120000011</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>929</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>929</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="12">
-        <v>2110000040</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="33" spans="1:5">
+      <c r="A15" s="13">
+        <v>2120000020</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>930</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>930</v>
       </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="14">
-        <v>2114000020</v>
-      </c>
-      <c r="B12" s="15" t="s">
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="33" spans="1:5">
+      <c r="A16" s="15">
+        <v>2120000030</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>931</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>931</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="33" spans="1:5">
-      <c r="A13" s="12">
-        <v>2120000010</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="13">
+        <v>2120000040</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>932</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>932</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="33" spans="1:5">
-      <c r="A14" s="14">
-        <v>2120000011</v>
-      </c>
-      <c r="B14" s="15" t="s">
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="33" spans="1:5">
+      <c r="A18" s="15">
+        <v>2120000060</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>933</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>933</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="33" spans="1:5">
-      <c r="A15" s="12">
-        <v>2120000020</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="33" spans="1:5">
+      <c r="A19" s="13">
+        <v>2120000080</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>934</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>934</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="33" spans="1:5">
-      <c r="A16" s="14">
-        <v>2120000030</v>
-      </c>
-      <c r="B16" s="15" t="s">
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="13">
+        <v>2140000020</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>927</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>927</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="15">
+        <v>2140000030</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>935</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>935</v>
       </c>
-      <c r="D16" s="3">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="12">
-        <v>2120000040</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="13">
+        <v>2140000040</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>936</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C22" s="14" t="s">
         <v>936</v>
       </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="33" spans="1:5">
-      <c r="A18" s="14">
-        <v>2120000060</v>
-      </c>
-      <c r="B18" s="15" t="s">
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="15">
+        <v>2140000050</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>937</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>937</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="33" spans="1:5">
-      <c r="A19" s="12">
-        <v>2120000080</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="13">
+        <v>2140000060</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>938</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C24" s="14" t="s">
         <v>938</v>
       </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="12">
-        <v>2140000020</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>931</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>931</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="14">
-        <v>2140000030</v>
-      </c>
-      <c r="B21" s="15" t="s">
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="15">
+        <v>2140000070</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>939</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>939</v>
       </c>
-      <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="12">
-        <v>2140000040</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="33" spans="1:5">
+      <c r="A26" s="13">
+        <v>2140000080</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="14">
-        <v>2140000050</v>
-      </c>
-      <c r="B23" s="15" t="s">
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="15">
+        <v>2140000110</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>941</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>941</v>
       </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="12">
-        <v>2140000060</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="13">
+        <v>2140000140</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>942</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C28" s="14" t="s">
         <v>942</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="14">
-        <v>2140000070</v>
-      </c>
-      <c r="B25" s="15" t="s">
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="33" spans="1:5">
+      <c r="A29" s="15">
+        <v>2140000150</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>943</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C29" s="16" t="s">
+        <v>944</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="33" spans="1:5">
+      <c r="A30" s="15">
+        <v>2140000160</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>943</v>
       </c>
-      <c r="D25" s="3">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="33" spans="1:5">
-      <c r="A26" s="12">
-        <v>2140000080</v>
-      </c>
-      <c r="B26" s="13" t="s">
+      <c r="C30" s="16" t="s">
         <v>944</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>944</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="14">
-        <v>2140000110</v>
-      </c>
-      <c r="B27" s="15" t="s">
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="15">
+        <v>2140000170</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>945</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C31" s="16" t="s">
         <v>945</v>
       </c>
-      <c r="D27" s="3">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="12">
-        <v>2140000140</v>
-      </c>
-      <c r="B28" s="13" t="s">
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="13">
+        <v>2140000180</v>
+      </c>
+      <c r="B32" s="14" t="s">
         <v>946</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>946</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="33" spans="1:5">
-      <c r="A29" s="14">
-        <v>2140000150</v>
-      </c>
-      <c r="B29" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>947</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="33" spans="1:5">
+      <c r="A33" s="15">
+        <v>2150000010</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>948</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="33" spans="1:5">
-      <c r="A30" s="14">
-        <v>2140000170</v>
-      </c>
-      <c r="B30" s="15" t="s">
+      <c r="C33" s="16" t="s">
+        <v>948</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="33" spans="1:5">
+      <c r="A34" s="13">
+        <v>2150000020</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>949</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C34" s="14" t="s">
+        <v>949</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="13">
+        <v>2150000060</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>950</v>
       </c>
-      <c r="D30" s="3">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="12">
-        <v>2140000180</v>
-      </c>
-      <c r="B31" s="13" t="s">
+      <c r="C35" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="15">
+        <v>2150000070</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>951</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C36" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="13">
+        <v>2150000080</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>952</v>
       </c>
-      <c r="D31" s="3">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="33" spans="1:5">
-      <c r="A32" s="14">
-        <v>2150000010</v>
-      </c>
-      <c r="B32" s="15" t="s">
+      <c r="C37" s="14" t="s">
+        <v>952</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="15">
+        <v>2150000090</v>
+      </c>
+      <c r="B38" s="16" t="s">
         <v>953</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C38" s="16" t="s">
         <v>953</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="33" spans="1:5">
-      <c r="A33" s="12">
-        <v>2150000020</v>
-      </c>
-      <c r="B33" s="13" t="s">
+      <c r="D38" s="4">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="13">
+        <v>2150000091</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="15">
+        <v>2150000100</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>954</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C40" s="16" t="s">
         <v>954</v>
       </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="12">
-        <v>2150000060</v>
-      </c>
-      <c r="B34" s="13" t="s">
+      <c r="D40" s="4">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="33" spans="1:5">
+      <c r="A41" s="13">
+        <v>2150000110</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>955</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>955</v>
       </c>
-      <c r="D34" s="3">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="14">
-        <v>2150000070</v>
-      </c>
-      <c r="B35" s="15" t="s">
+      <c r="D41" s="4">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="13">
+        <v>2150100060</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="15">
+        <v>2150100070</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="13">
+        <v>2150100080</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>952</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>952</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="15">
+        <v>2150100090</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="13">
+        <v>2150100091</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="15">
+        <v>2150200060</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>950</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>950</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="13">
+        <v>2150200070</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>951</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>951</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="15">
+        <v>2150200080</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>952</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>952</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="13">
+        <v>2150200090</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="D50" s="4">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="15">
+        <v>2150200091</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="D51" s="4">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="13">
+        <v>2150300060</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="15">
+        <v>2150300070</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="13">
+        <v>2150300090</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="15">
+        <v>2150300091</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="13">
+        <v>2150400060</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>950</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="15">
+        <v>2150400090</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="13">
+        <v>2150400091</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="13">
+        <v>2340000010</v>
+      </c>
+      <c r="B59" s="14" t="s">
         <v>956</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C59" s="14" t="s">
         <v>956</v>
       </c>
-      <c r="D35" s="3">
-        <v>0</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="12">
-        <v>2150000080</v>
-      </c>
-      <c r="B36" s="13" t="s">
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="15">
+        <v>2340000020</v>
+      </c>
+      <c r="B60" s="16" t="s">
         <v>957</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C60" s="16" t="s">
+        <v>958</v>
+      </c>
+      <c r="D60" s="4">
+        <v>2</v>
+      </c>
+      <c r="E60" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="13">
+        <v>2340000030</v>
+      </c>
+      <c r="B61" s="14" t="s">
         <v>957</v>
       </c>
-      <c r="D36" s="3">
-        <v>0</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="14">
-        <v>2150000090</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="D37" s="3">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="12">
-        <v>2150000091</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="14">
-        <v>2150000100</v>
-      </c>
-      <c r="B39" s="15" t="s">
+      <c r="C61" s="14" t="s">
         <v>959</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>959</v>
-      </c>
-      <c r="D39" s="3">
-        <v>0</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="33" spans="1:5">
-      <c r="A40" s="12">
-        <v>2150000110</v>
-      </c>
-      <c r="B40" s="13" t="s">
+      <c r="D61" s="4">
+        <v>2</v>
+      </c>
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="15">
+        <v>2340000040</v>
+      </c>
+      <c r="B62" s="16" t="s">
         <v>960</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C62" s="16" t="s">
         <v>960</v>
       </c>
-      <c r="D40" s="3">
-        <v>0</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="12">
-        <v>2150100060</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="D41" s="3">
-        <v>0</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="14">
-        <v>2150100070</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="12">
-        <v>2150100080</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>957</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>957</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="14">
-        <v>2150100090</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="12">
-        <v>2150100091</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="14">
-        <v>2150200060</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>955</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>955</v>
-      </c>
-      <c r="D46" s="3">
-        <v>0</v>
-      </c>
-      <c r="E46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="12">
-        <v>2150200070</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>956</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>956</v>
-      </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="14">
-        <v>2150200080</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>957</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>957</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="12">
-        <v>2150200090</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="14">
-        <v>2150200091</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="D50" s="3">
-        <v>0</v>
-      </c>
-      <c r="E50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="12">
-        <v>2150300060</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="D51" s="3">
-        <v>0</v>
-      </c>
-      <c r="E51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="14">
-        <v>2150300070</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="12">
-        <v>2150300090</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="14">
-        <v>2150300091</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="D54" s="3">
-        <v>0</v>
-      </c>
-      <c r="E54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="12">
-        <v>2150400060</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>955</v>
-      </c>
-      <c r="D55" s="3">
-        <v>0</v>
-      </c>
-      <c r="E55" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="14">
-        <v>2150400090</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="D56" s="3">
-        <v>0</v>
-      </c>
-      <c r="E56" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="12">
-        <v>2150400091</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>958</v>
-      </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="12">
-        <v>2340000010</v>
-      </c>
-      <c r="B58" s="13" t="s">
+      <c r="D62" s="4">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="13">
+        <v>2340000050</v>
+      </c>
+      <c r="B63" s="14" t="s">
         <v>961</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C63" s="14" t="s">
         <v>961</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="14">
-        <v>2340000020</v>
-      </c>
-      <c r="B59" s="15" t="s">
+      <c r="D63" s="4">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="15">
+        <v>2340000080</v>
+      </c>
+      <c r="B64" s="16" t="s">
         <v>962</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C64" s="16" t="s">
+        <v>962</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="13">
+        <v>3140000020</v>
+      </c>
+      <c r="B65" s="14" t="s">
         <v>963</v>
       </c>
-      <c r="D59" s="3">
-        <v>2</v>
-      </c>
-      <c r="E59" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="12">
-        <v>2340000030</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>962</v>
-      </c>
-      <c r="C60" s="13" t="s">
+      <c r="C65" s="14" t="s">
+        <v>963</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="15">
+        <v>3140000030</v>
+      </c>
+      <c r="B66" s="16" t="s">
         <v>964</v>
       </c>
-      <c r="D60" s="3">
-        <v>2</v>
-      </c>
-      <c r="E60" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="14">
-        <v>2340000040</v>
-      </c>
-      <c r="B61" s="15" t="s">
+      <c r="C66" s="16" t="s">
+        <v>964</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="13">
+        <v>3140000040</v>
+      </c>
+      <c r="B67" s="14" t="s">
         <v>965</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C67" s="14" t="s">
         <v>965</v>
       </c>
-      <c r="D61" s="3">
-        <v>0</v>
-      </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="12">
-        <v>2340000050</v>
-      </c>
-      <c r="B62" s="13" t="s">
+      <c r="D67" s="4">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:5">
+      <c r="A68" s="2">
+        <v>2140000100</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C68" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="14">
-        <v>2340000080</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>967</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>967</v>
-      </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="12">
-        <v>3140000020</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>968</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>968</v>
-      </c>
-      <c r="D64" s="3">
-        <v>0</v>
-      </c>
-      <c r="E64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="14">
-        <v>3140000030</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>969</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>969</v>
-      </c>
-      <c r="D65" s="3">
-        <v>0</v>
-      </c>
-      <c r="E65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="12">
-        <v>3140000040</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>970</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>970</v>
-      </c>
-      <c r="D66" s="3">
-        <v>0</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
         <v>0</v>
       </c>
     </row>
